--- a/data/trans_orig/IP31KM02_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79610</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69326</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>88657</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61373</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>52335</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69967</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>62136</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71491</t>
+          <t>53887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96085</t>
+          <t>70222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>146327</t>
+          <t>141746</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131178</t>
+          <t>128742</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160890</t>
+          <t>152899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41599</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32552</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51883</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40336</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31742</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49374</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>39,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>30127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63685</t>
+          <t>46462</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90559</t>
+          <t>79812</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75996</t>
+          <t>68659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105708</t>
+          <t>92816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53771</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44978</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61787</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>59,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53746</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>45125</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>61178</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>48,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54538</t>
+          <t>55867</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45127</t>
+          <t>47053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62826</t>
+          <t>63431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>108285</t>
+          <t>109638</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96677</t>
+          <t>97721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119030</t>
+          <t>121169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36109</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28093</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44902</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>40,17%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39646</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32214</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>48267</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>42,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>51,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39170</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30882</t>
+          <t>31979</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48581</t>
+          <t>48357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>78816</t>
+          <t>75652</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68071</t>
+          <t>64121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90424</t>
+          <t>87569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33777</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27506</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39985</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>71,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>31782</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25213</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37544</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36130</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>25244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>38857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>67911</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57629</t>
+          <t>56629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77198</t>
+          <t>74729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22067</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15859</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28338</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18307</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12545</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24876</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33355</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>41518</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35224</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54793</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>109041</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>93845</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>122133</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>47,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>61,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>94900</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63541</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>115068</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>114476</t>
+          <t>89693</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97707</t>
+          <t>78298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>209376</t>
+          <t>198734</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163713</t>
+          <t>180390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232073</t>
+          <t>218093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88272</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75180</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103468</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>120637</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>100469</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>151996</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>98182</t>
+          <t>86947</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>76034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114951</t>
+          <t>98342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>218820</t>
+          <t>175219</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196123</t>
+          <t>155860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264483</t>
+          <t>193563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88200</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70588</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>100405</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>72695</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>63940</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>82003</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>62,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>55,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>95790</t>
+          <t>72850</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72741</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108612</t>
+          <t>81012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>168486</t>
+          <t>161050</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143036</t>
+          <t>139558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>182892</t>
+          <t>175183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57386</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>45181</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>74998</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>42814</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>33506</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>51569</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63671</t>
+          <t>42616</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50849</t>
+          <t>34454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86720</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>106484</t>
+          <t>100002</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92078</t>
+          <t>85869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131934</t>
+          <t>121494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>39493</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>32579</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46713</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>59,96%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>44995</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>37956</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>51130</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>65,31%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>55,09%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>74,21%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>47826</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47473</t>
+          <t>53693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>87319</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74498</t>
+          <t>76786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95780</t>
+          <t>96759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19150</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>33284</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>40,04%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>50,54%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>23900</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17765</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>30939</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>25,79%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>44,91%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>48901</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42145</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>59434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>403891</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>377292</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>428499</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>59,77%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>55,84%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>533</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>359490</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>306944</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>386359</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>55,72%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>59,89%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>426174</t>
+          <t>360931</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>397381</t>
+          <t>338730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>453081</t>
+          <t>379008</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>785664</t>
+          <t>764823</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>729070</t>
+          <t>733335</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>826440</t>
+          <t>798033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>271804</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>247196</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>298403</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44,16%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>369</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>285641</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>258772</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>338187</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>44,28%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>40,11%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>52,42%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>306194</t>
+          <t>249301</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>279287</t>
+          <t>231224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>334987</t>
+          <t>271502</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>591835</t>
+          <t>521104</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>551059</t>
+          <t>487894</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>648429</t>
+          <t>552592</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
